--- a/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 16,23</t>
+          <t>3,66; 16,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,07</t>
+          <t>3,09; 17,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 16,79</t>
+          <t>4,36; 17,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,98</t>
+          <t>2,52; 14,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 24,41</t>
+          <t>7,57; 23,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,83</t>
+          <t>1,33; 13,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 22,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 12,18</t>
+          <t>4,23; 12,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 18,4</t>
+          <t>6,85; 17,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,77</t>
+          <t>4,15; 12,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,79</t>
+          <t>0,0; 14,06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 18,0</t>
+          <t>6,77; 17,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,79</t>
+          <t>2,37; 10,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,04</t>
+          <t>3,46; 13,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 40,38</t>
+          <t>5,56; 40,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,56</t>
+          <t>4,7; 14,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,01</t>
+          <t>4,04; 12,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 15,02</t>
+          <t>4,91; 14,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,44</t>
+          <t>0,0; 17,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 14,11</t>
+          <t>6,8; 13,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,77</t>
+          <t>4,09; 10,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,24</t>
+          <t>5,33; 12,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 23,0</t>
+          <t>3,81; 21,73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,16</t>
+          <t>1,06; 10,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,96</t>
+          <t>3,06; 14,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 20,39</t>
+          <t>6,15; 20,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,48</t>
+          <t>0,93; 9,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 23,17</t>
+          <t>8,81; 22,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 17,06</t>
+          <t>4,44; 16,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,84</t>
+          <t>0,0; 16,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,16</t>
+          <t>1,96; 7,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,75</t>
+          <t>7,11; 15,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 16,1</t>
+          <t>6,56; 16,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,01</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,94</t>
+          <t>1,76; 11,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,62</t>
+          <t>3,61; 14,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,68</t>
+          <t>1,41; 12,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,91</t>
+          <t>0,0; 33,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,81</t>
+          <t>2,79; 12,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 14,19</t>
+          <t>3,46; 14,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,23</t>
+          <t>0,78; 7,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,13</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,78</t>
+          <t>3,07; 9,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,54</t>
+          <t>4,62; 11,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,75</t>
+          <t>1,46; 7,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,56</t>
+          <t>1,66; 22,27</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 18,78</t>
+          <t>2,03; 18,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,05</t>
+          <t>1,81; 16,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,87</t>
+          <t>1,42; 13,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,69</t>
+          <t>0,0; 14,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,86</t>
+          <t>1,57; 14,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 18,14</t>
+          <t>3,22; 17,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,4</t>
+          <t>2,95; 13,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,64</t>
+          <t>2,56; 12,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 13,68</t>
+          <t>3,57; 12,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,84</t>
+          <t>1,39; 12,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 19,62</t>
+          <t>5,17; 19,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 26,56</t>
+          <t>8,96; 27,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,76</t>
+          <t>0,0; 43,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,19</t>
+          <t>1,22; 11,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 19,21</t>
+          <t>5,08; 20,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 26,38</t>
+          <t>8,93; 25,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 11,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,44</t>
+          <t>2,51; 10,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 16,92</t>
+          <t>6,5; 16,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 23,01</t>
+          <t>10,85; 22,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 17,49</t>
+          <t>1,31; 16,03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,15</t>
+          <t>2,9; 9,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 18,41</t>
+          <t>8,38; 18,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 21,96</t>
+          <t>10,75; 22,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 22,75</t>
+          <t>1,8; 23,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,17</t>
+          <t>5,07; 13,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 17,44</t>
+          <t>8,34; 17,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,04; 22,4</t>
+          <t>10,56; 21,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,86</t>
+          <t>4,53; 10,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 16,31</t>
+          <t>9,61; 16,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,77; 19,69</t>
+          <t>11,49; 19,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,5</t>
+          <t>0,82; 11,54</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 20,51</t>
+          <t>9,99; 20,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,64</t>
+          <t>8,97; 18,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,22</t>
+          <t>3,69; 9,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,96</t>
+          <t>0,0; 20,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,17</t>
+          <t>10,51; 20,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,28</t>
+          <t>4,49; 11,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,91</t>
+          <t>2,87; 8,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,49</t>
+          <t>0,0; 23,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,36</t>
+          <t>11,53; 18,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,07</t>
+          <t>7,69; 13,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,31</t>
+          <t>4,11; 8,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 18,45</t>
+          <t>2,18; 16,8</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,52</t>
+          <t>6,86; 10,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,86</t>
+          <t>7,97; 11,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,4</t>
+          <t>7,51; 11,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,66</t>
+          <t>3,62; 12,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,17</t>
+          <t>6,64; 10,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,31</t>
+          <t>8,19; 11,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,76</t>
+          <t>7,07; 10,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,47</t>
+          <t>1,93; 7,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,94</t>
+          <t>7,18; 9,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,22</t>
+          <t>8,65; 11,42</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,46</t>
+          <t>7,84; 10,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,11</t>
+          <t>3,53; 8,14</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7593</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12003</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7727</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1836; 8205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1504; 8384</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2268; 9239</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7339</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4116; 12693</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>725; 7301</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3198</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4328; 12523</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7058; 18174</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4423; 13812</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3677</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10545</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8004</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18549</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12520</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14904</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6195; 16148</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2261; 10064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3011; 11909</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>758; 5472</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4540; 13932</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3927; 12581</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4565; 13887</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2844</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12797; 25964</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7871; 19294</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9599; 21951</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1141; 6511</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7664</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10677</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15811</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13360</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>673; 6622</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2062; 10048</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4009; 13426</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>623; 6238</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6279; 16200</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2790; 10170</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2767</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2564; 9538</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9861; 22044</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8395; 20719</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3691</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5654</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5998</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7819</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11652</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5445</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1184; 7532</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2611; 10214</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1024; 8936</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4480</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1888; 8724</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2742; 11655</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>619; 6216</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3578</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4156; 12866</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7004; 17816</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2215; 11030</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>463; 6229</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6261</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>650; 6076</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700; 6291</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>594; 5579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4759</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>678; 6132</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1444; 7891</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1894; 8410</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2098; 9941</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3097; 10703</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8315</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12411</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>709; 6257</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2819; 10895</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4624; 13949</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3979</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>620; 5652</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3000; 12276</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5093; 14436</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 1897</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2554; 10800</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7388; 18689</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>11779; 24328</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>343; 4197</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6931</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17030</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17398</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10341</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>17808</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>17690</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>17272</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>34838</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>35088</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3522; 11893</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11317; 24457</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11993; 24657</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>401; 5227</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6282; 16482</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11934; 24576</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11875; 24641</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>11121; 24863</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>26727; 45007</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>25733; 43962</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>408; 5770</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>17825</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>19448</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10033</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>19762</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>12188</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>37587</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>31636</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>18873</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2262</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>12056; 24940</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>13632; 27942</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5852; 15485</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2457</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>14045; 27473</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>7181; 18428</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4759; 14279</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4691</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>29320; 46917</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>23991; 41245</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>13323; 27889</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>696; 5362</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>51127</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>65108</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>60248</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>103313</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>135927</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>118869</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>41000; 62606</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>52879; 77802</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>48061; 73365</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3635; 12644</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>41419; 64291</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>57925; 84753</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>47364; 70654</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2536; 9440</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>87795; 118659</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>118617; 156587</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>102744; 138204</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>8178; 18872</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,33</t>
+          <t>3,67; 16,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,23</t>
+          <t>3,2; 17,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 17,77</t>
+          <t>4,49; 16,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,11</t>
+          <t>2,53; 14,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 23,35</t>
+          <t>7,43; 24,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,37</t>
+          <t>1,51; 12,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,74</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,25</t>
+          <t>4,09; 12,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 17,64</t>
+          <t>7,28; 18,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,96</t>
+          <t>3,88; 12,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,06</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 17,64</t>
+          <t>6,8; 17,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,56</t>
+          <t>2,6; 10,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,66</t>
+          <t>3,67; 13,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 40,15</t>
+          <t>5,61; 42,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,41</t>
+          <t>4,09; 13,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,93</t>
+          <t>3,96; 12,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 14,92</t>
+          <t>4,64; 14,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,41</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,79</t>
+          <t>6,72; 13,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,02</t>
+          <t>4,19; 10,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 12,18</t>
+          <t>5,44; 12,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 21,73</t>
+          <t>4,12; 22,39</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,45</t>
+          <t>1,06; 9,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,91</t>
+          <t>2,96; 14,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 20,58</t>
+          <t>6,17; 20,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,29</t>
+          <t>0,95; 8,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 22,74</t>
+          <t>9,49; 23,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,19</t>
+          <t>4,42; 16,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,85</t>
+          <t>0,0; 20,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,31</t>
+          <t>1,96; 7,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 15,9</t>
+          <t>7,61; 16,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,18</t>
+          <t>6,56; 15,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>0,0; 10,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,18</t>
+          <t>1,97; 11,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 14,12</t>
+          <t>3,19; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,31</t>
+          <t>1,41; 11,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,76</t>
+          <t>0,0; 34,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,87</t>
+          <t>2,76; 12,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 14,71</t>
+          <t>3,56; 13,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,85</t>
+          <t>0,81; 8,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,35</t>
+          <t>0,0; 24,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,52</t>
+          <t>2,91; 9,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,75</t>
+          <t>4,09; 11,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,27</t>
+          <t>1,45; 7,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 22,27</t>
+          <t>1,73; 21,13</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 18,92</t>
+          <t>2,01; 18,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,3</t>
+          <t>1,85; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,34</t>
+          <t>1,39; 13,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,79</t>
+          <t>0,0; 12,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,17</t>
+          <t>1,55; 14,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 17,58</t>
+          <t>3,14; 17,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 13,08</t>
+          <t>2,96; 12,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 12,14</t>
+          <t>2,59; 12,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,35</t>
+          <t>3,6; 12,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,24</t>
+          <t>1,39; 13,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 19,98</t>
+          <t>5,31; 19,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 27,04</t>
+          <t>8,86; 25,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,57</t>
+          <t>0,0; 42,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,12</t>
+          <t>1,23; 12,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 20,78</t>
+          <t>5,04; 19,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 25,32</t>
+          <t>8,06; 24,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,6</t>
+          <t>2,42; 9,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,45</t>
+          <t>6,87; 17,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,85; 22,4</t>
+          <t>10,67; 22,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 16,03</t>
+          <t>1,31; 16,51</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1557,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,78</t>
+          <t>2,84; 9,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 18,11</t>
+          <t>8,34; 17,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 22,1</t>
+          <t>10,85; 21,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 23,45</t>
+          <t>1,8; 25,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 13,31</t>
+          <t>4,91; 12,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,17</t>
+          <t>8,23; 17,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,92</t>
+          <t>10,61; 22,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,13</t>
+          <t>4,88; 9,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,18</t>
+          <t>9,24; 15,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,63</t>
+          <t>12,11; 19,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 11,54</t>
+          <t>0,83; 13,48</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,67</t>
+          <t>9,96; 20,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,39</t>
+          <t>8,73; 16,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,77</t>
+          <t>3,86; 10,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,51</t>
+          <t>0,0; 21,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,51; 20,57</t>
+          <t>10,58; 20,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,51</t>
+          <t>4,41; 11,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,62</t>
+          <t>2,84; 8,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,52</t>
+          <t>0,0; 24,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,53; 18,46</t>
+          <t>11,78; 18,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,22</t>
+          <t>7,7; 13,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,6</t>
+          <t>3,99; 8,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,8</t>
+          <t>2,25; 19,12</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,47</t>
+          <t>7,05; 10,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,72</t>
+          <t>8,12; 11,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,46</t>
+          <t>7,65; 11,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,6</t>
+          <t>3,76; 12,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,3</t>
+          <t>6,67; 10,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,19; 11,98</t>
+          <t>8,25; 12,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,55</t>
+          <t>7,16; 10,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,17</t>
+          <t>1,92; 7,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,71</t>
+          <t>7,27; 9,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,42</t>
+          <t>8,68; 11,36</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,55</t>
+          <t>7,84; 10,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,14</t>
+          <t>3,33; 8,02</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1836; 8205</t>
+          <t>1844; 8044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1504; 8384</t>
+          <t>1558; 8412</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2268; 9239</t>
+          <t>2336; 8808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1313; 7339</t>
+          <t>1317; 7324</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4116; 12693</t>
+          <t>4038; 13366</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>725; 7301</t>
+          <t>826; 6981</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3198</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4328; 12523</t>
+          <t>4186; 12953</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7058; 18174</t>
+          <t>7495; 18850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4423; 13812</t>
+          <t>4141; 12802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3677</t>
+          <t>0; 3817</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6195; 16148</t>
+          <t>6228; 15780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2261; 10064</t>
+          <t>2478; 10215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3011; 11909</t>
+          <t>3198; 11821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>758; 5472</t>
+          <t>764; 5757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4540; 13932</t>
+          <t>3954; 12722</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3927; 12581</t>
+          <t>3854; 12391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4565; 13887</t>
+          <t>4322; 13840</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2844</t>
+          <t>0; 2848</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12797; 25964</t>
+          <t>12650; 25607</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7871; 19294</t>
+          <t>8061; 19487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9599; 21951</t>
+          <t>9798; 22587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1141; 6511</t>
+          <t>1234; 6709</t>
         </is>
       </c>
     </row>
@@ -2625,17 +2625,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>673; 6622</t>
+          <t>671; 6305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2062; 10048</t>
+          <t>1994; 9589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4009; 13426</t>
+          <t>4024; 13290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2645,42 +2645,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>623; 6238</t>
+          <t>636; 5666</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6279; 16200</t>
+          <t>6762; 16552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2790; 10170</t>
+          <t>2774; 10384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2767</t>
+          <t>0; 3327</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2564; 9538</t>
+          <t>2555; 9836</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9861; 22044</t>
+          <t>10555; 22729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8395; 20719</t>
+          <t>8404; 19841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3305</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1184; 7532</t>
+          <t>1330; 7677</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2611; 10214</t>
+          <t>2311; 10248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024; 8936</t>
+          <t>1028; 8431</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 4563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1888; 8724</t>
+          <t>1870; 8776</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2742; 11655</t>
+          <t>2824; 10836</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>619; 6216</t>
+          <t>639; 6434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>0; 3575</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4156; 12866</t>
+          <t>3938; 13280</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7004; 17816</t>
+          <t>6201; 17195</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2215; 11030</t>
+          <t>2201; 11277</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>463; 6229</t>
+          <t>485; 5908</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>650; 6076</t>
+          <t>647; 6099</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>700; 6291</t>
+          <t>712; 6757</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>594; 5579</t>
+          <t>579; 5454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>678; 6132</t>
+          <t>672; 6152</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1444; 7891</t>
+          <t>1410; 7721</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1894; 8410</t>
+          <t>1901; 7893</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2098; 9941</t>
+          <t>2124; 9958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3097; 10703</t>
+          <t>3124; 11123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>709; 6257</t>
+          <t>708; 6764</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2819; 10895</t>
+          <t>2894; 10791</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4624; 13949</t>
+          <t>4572; 13181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3979</t>
+          <t>0; 3925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>620; 5652</t>
+          <t>625; 6199</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3000; 12276</t>
+          <t>2976; 11792</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5093; 14436</t>
+          <t>4598; 13979</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>0; 1663</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2554; 10800</t>
+          <t>2464; 9781</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7388; 18689</t>
+          <t>7805; 19310</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11779; 24328</t>
+          <t>11583; 24514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>343; 4197</t>
+          <t>344; 4323</t>
         </is>
       </c>
     </row>
@@ -3457,37 +3457,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3522; 11893</t>
+          <t>3448; 12051</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11317; 24457</t>
+          <t>11265; 24115</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11993; 24657</t>
+          <t>12102; 24374</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>401; 5227</t>
+          <t>402; 5766</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6282; 16482</t>
+          <t>6081; 15965</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11934; 24576</t>
+          <t>11777; 25738</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11875; 24641</t>
+          <t>11923; 25127</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11121; 24863</t>
+          <t>11982; 24238</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26727; 45007</t>
+          <t>25696; 44206</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25733; 43962</t>
+          <t>27131; 44388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>408; 5770</t>
+          <t>415; 6743</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12056; 24940</t>
+          <t>12022; 24406</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13632; 27942</t>
+          <t>13270; 25757</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5852; 15485</t>
+          <t>6114; 16282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2457</t>
+          <t>0; 2553</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14045; 27473</t>
+          <t>14127; 27796</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7181; 18428</t>
+          <t>7064; 18302</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4759; 14279</t>
+          <t>4704; 14316</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4691</t>
+          <t>0; 4921</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29320; 46917</t>
+          <t>29945; 48158</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23991; 41245</t>
+          <t>24023; 41121</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13323; 27889</t>
+          <t>12939; 26506</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>696; 5362</t>
+          <t>717; 6103</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>41000; 62606</t>
+          <t>42169; 63698</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52879; 77802</t>
+          <t>53923; 77796</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48061; 73365</t>
+          <t>49014; 74082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3635; 12644</t>
+          <t>3769; 12784</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>41419; 64291</t>
+          <t>41648; 64459</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57925; 84753</t>
+          <t>58366; 85503</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47364; 70654</t>
+          <t>47953; 72760</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2536; 9440</t>
+          <t>2529; 10005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87795; 118659</t>
+          <t>88837; 120141</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118617; 156587</t>
+          <t>119009; 155819</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102744; 138204</t>
+          <t>102758; 135141</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8178; 18872</t>
+          <t>7716; 18602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7,43%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,01</t>
+          <t>2,44; 13,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 17,29</t>
+          <t>7,56; 24,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,94</t>
+          <t>1,4; 12,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 26,52</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,36; 16,23</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,14; 17,07</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,51; 16,79</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 14,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,43; 24,59</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 12,78</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,67</t>
+          <t>4,12; 12,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 18,3</t>
+          <t>6,67; 18,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,01</t>
+          <t>3,89; 11,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,59</t>
+          <t>0,0; 13,74</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,52%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 17,24</t>
+          <t>4,27; 13,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,72</t>
+          <t>4,01; 13,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,56</t>
+          <t>5,15; 15,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 42,24</t>
+          <t>0,0; 16,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,16</t>
+          <t>6,99; 18,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,74</t>
+          <t>2,27; 10,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,87</t>
+          <t>3,78; 14,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,44</t>
+          <t>5,26; 40,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,6</t>
+          <t>6,95; 14,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,12</t>
+          <t>4,05; 9,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,53</t>
+          <t>5,44; 12,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 22,39</t>
+          <t>3,83; 22,74</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,62%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,75%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,95</t>
+          <t>0,94; 8,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 14,22</t>
+          <t>8,8; 23,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 20,37</t>
+          <t>4,41; 17,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 19,22</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,07; 10,16</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,96; 13,96</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,19; 20,39</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 8,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,49; 23,23</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,42; 16,53</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,26</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,54</t>
+          <t>2,0; 8,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,39</t>
+          <t>7,32; 16,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 15,5</t>
+          <t>6,38; 16,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,88</t>
+          <t>0,0; 9,96</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,39</t>
+          <t>2,73; 12,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,17</t>
+          <t>3,58; 14,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,61</t>
+          <t>0,78; 8,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 23,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,95</t>
+          <t>1,75; 10,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,68</t>
+          <t>3,53; 14,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,13</t>
+          <t>1,4; 11,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>0,0; 34,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,83</t>
+          <t>3,08; 9,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,35</t>
+          <t>4,59; 12,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,43</t>
+          <t>1,29; 7,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 21,13</t>
+          <t>1,35; 21,28</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,99</t>
+          <t>0,0; 14,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 17,5</t>
+          <t>1,57; 15,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,04</t>
+          <t>3,09; 18,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,63</t>
+          <t>2,1; 18,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,21</t>
+          <t>1,82; 16,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,2</t>
+          <t>1,4; 12,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,28</t>
+          <t>2,12; 12,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,16</t>
+          <t>2,64; 11,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,83</t>
+          <t>3,73; 13,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>11,33%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16,12%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,23</t>
+          <t>1,22; 11,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 19,79</t>
+          <t>4,96; 19,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,86; 25,55</t>
+          <t>8,92; 26,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,98</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,2</t>
+          <t>1,39; 11,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,96</t>
+          <t>5,57; 19,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,51</t>
+          <t>8,98; 26,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 35,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,6</t>
+          <t>2,44; 9,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 17,0</t>
+          <t>6,75; 16,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 22,57</t>
+          <t>10,67; 23,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 16,51</t>
+          <t>1,04; 18,42</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15,73%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>12,61%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15,6%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,91</t>
+          <t>5,1; 13,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,86</t>
+          <t>7,96; 17,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 21,85</t>
+          <t>11,04; 22,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 25,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 12,89</t>
+          <t>2,82; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,99</t>
+          <t>8,62; 18,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 22,35</t>
+          <t>10,58; 21,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,77; 26,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,87</t>
+          <t>4,55; 9,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,89</t>
+          <t>9,66; 16,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,82</t>
+          <t>11,77; 19,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 13,48</t>
+          <t>0,71; 10,85</t>
         </is>
       </c>
     </row>
@@ -1629,49 +1629,49 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>14,78%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>12,8%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14,79%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,96; 20,23</t>
+          <t>9,77; 20,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 16,95</t>
+          <t>4,6; 12,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,28</t>
+          <t>2,8; 8,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,31</t>
+          <t>0,0; 26,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,58; 20,81</t>
+          <t>10,35; 20,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,43</t>
+          <t>9,23; 17,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,64</t>
+          <t>3,71; 10,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,68</t>
+          <t>0,0; 18,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,78; 18,94</t>
+          <t>11,33; 18,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,18</t>
+          <t>7,55; 13,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,18</t>
+          <t>4,1; 8,31</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,12</t>
+          <t>2,25; 18,35</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,65</t>
+          <t>6,59; 10,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,72</t>
+          <t>8,26; 12,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,57</t>
+          <t>6,86; 10,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,74</t>
+          <t>1,87; 7,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,33</t>
+          <t>6,81; 10,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,08</t>
+          <t>7,98; 11,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,86</t>
+          <t>7,76; 11,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,6</t>
+          <t>3,45; 12,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,83</t>
+          <t>7,2; 9,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,36</t>
+          <t>8,61; 11,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,32</t>
+          <t>7,91; 10,46</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,02</t>
+          <t>3,35; 8,23</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,44 +2141,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4260</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4271</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4741</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3333</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7732</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7593</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>927</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1844; 8044</t>
+          <t>1272; 7271</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1558; 8412</t>
+          <t>4112; 13267</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2336; 8808</t>
+          <t>764; 7010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 3230</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2191; 8154</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1527; 8307</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2345; 8727</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1317; 7324</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4038; 13366</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>826; 6981</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4042</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4186; 12953</t>
+          <t>4217; 12460</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7495; 18850</t>
+          <t>6869; 18951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4141; 12802</t>
+          <t>4147; 12548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3817</t>
+          <t>0; 3200</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8004</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5037</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6485</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8004</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7483</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8420</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2788</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6228; 15780</t>
+          <t>4127; 13105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2478; 10215</t>
+          <t>3902; 12652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3198; 11821</t>
+          <t>4789; 13978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>764; 5757</t>
+          <t>0; 2351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3954; 12722</t>
+          <t>6398; 16481</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3854; 12391</t>
+          <t>2161; 10280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4322; 13840</t>
+          <t>3291; 12239</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2848</t>
+          <t>690; 5267</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12650; 25607</t>
+          <t>13078; 26567</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8061; 19487</t>
+          <t>7790; 18805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9798; 22587</t>
+          <t>9803; 22053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1234; 6709</t>
+          <t>1055; 6262</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,44 +2557,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10677</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2799</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5134</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>7664</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10677</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5695</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5305</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>524</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>671; 6305</t>
+          <t>634; 5696</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1994; 9589</t>
+          <t>6271; 16508</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4024; 13290</t>
+          <t>2769; 10712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 2699</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>676; 6436</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1993; 9409</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4035; 13299</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>636; 5666</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6762; 16552</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2774; 10384</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3327</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2555; 9836</t>
+          <t>2606; 10647</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10555; 22729</t>
+          <t>10152; 23220</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8404; 19841</t>
+          <t>8171; 20610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3305</t>
+          <t>0; 2750</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5998</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3400</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5654</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3225</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4419</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2220</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1879</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1330; 7677</t>
+          <t>1851; 8682</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2311; 10248</t>
+          <t>2833; 11240</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1028; 8431</t>
+          <t>616; 6510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1870; 8776</t>
+          <t>1179; 7375</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2824; 10836</t>
+          <t>2552; 10574</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>639; 6434</t>
+          <t>1014; 8485</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3575</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3938; 13280</t>
+          <t>4162; 13215</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6201; 17195</t>
+          <t>6958; 19010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2201; 11277</t>
+          <t>1956; 11754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>485; 5908</t>
+          <t>366; 5781</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,37 +2973,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2618</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2357</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2387</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>647; 6099</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>712; 6757</t>
+          <t>680; 6862</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>579; 5454</t>
+          <t>1387; 8143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4062</t>
+          <t>675; 6031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>672; 6152</t>
+          <t>704; 6197</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1410; 7721</t>
+          <t>585; 5381</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1901; 7893</t>
+          <t>1364; 7970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2124; 9958</t>
+          <t>2160; 9529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3124; 11123</t>
+          <t>3236; 11859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2748</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6177</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>8315</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6234</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>992</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1240</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>708; 6764</t>
+          <t>619; 5684</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2894; 10791</t>
+          <t>2928; 11352</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4572; 13181</t>
+          <t>5085; 15045</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 1566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>625; 6199</t>
+          <t>710; 6053</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2976; 11792</t>
+          <t>3037; 10701</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4598; 13979</t>
+          <t>4630; 13698</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1663</t>
+          <t>0; 3221</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2464; 9781</t>
+          <t>2485; 9626</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7805; 19310</t>
+          <t>7665; 19218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11583; 24514</t>
+          <t>11592; 24986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>344; 4323</t>
+          <t>245; 4330</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10341</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17808</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17690</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>6931</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>17030</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>17398</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10341</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>17808</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1932</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3448; 12051</t>
+          <t>6322; 16311</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11265; 24115</t>
+          <t>11398; 24957</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12102; 24374</t>
+          <t>12410; 25188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>402; 5766</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6081; 15965</t>
+          <t>3425; 12349</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11777; 25738</t>
+          <t>11636; 24858</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11923; 25127</t>
+          <t>11799; 24494</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>350; 5305</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11982; 24238</t>
+          <t>11169; 24212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25696; 44206</t>
+          <t>26860; 45351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27131; 44388</t>
+          <t>26358; 44110</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>415; 6743</t>
+          <t>336; 5174</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>19762</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12188</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>17825</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>19448</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>10033</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>19762</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12188</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8840</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>688</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2096</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12022; 24406</t>
+          <t>13044; 26936</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13270; 25757</t>
+          <t>7365; 19664</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6114; 16282</t>
+          <t>4638; 14759</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2553</t>
+          <t>0; 5173</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14127; 27796</t>
+          <t>12489; 24749</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7064; 18302</t>
+          <t>14023; 26810</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4704; 14316</t>
+          <t>5877; 16194</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4921</t>
+          <t>0; 2150</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29945; 48158</t>
+          <t>28815; 46666</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24023; 41121</t>
+          <t>23555; 40796</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12939; 26506</t>
+          <t>13300; 26929</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>717; 6103</t>
+          <t>693; 5656</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>70819</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>42169; 63698</t>
+          <t>41097; 63437</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53923; 77796</t>
+          <t>58462; 87104</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49014; 74082</t>
+          <t>45971; 72075</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3769; 12784</t>
+          <t>2282; 8806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>41648; 64459</t>
+          <t>40701; 62933</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58366; 85503</t>
+          <t>52968; 78747</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47953; 72760</t>
+          <t>49663; 72997</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2529; 10005</t>
+          <t>3298; 12315</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>88837; 120141</t>
+          <t>87981; 121498</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119009; 155819</t>
+          <t>118088; 153873</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102758; 135141</t>
+          <t>103583; 137035</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7716; 18602</t>
+          <t>7286; 17885</t>
         </is>
       </c>
     </row>
